--- a/hardware/BOM.xlsx
+++ b/hardware/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hamster\Documents\Development\Badges\dczia\mk9-badge\hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AE1892-83DF-4DFD-8F58-6AE0A8227181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8966293E-EBF9-43E3-973D-AA976C767EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39740" yWindow="1830" windowWidth="27410" windowHeight="17230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44300" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="112">
   <si>
     <t>Part Number</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Feeder</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>W25Q128JVSIM</t>
   </si>
   <si>
@@ -366,6 +363,12 @@
   </si>
   <si>
     <t>Badge Run, units</t>
+  </si>
+  <si>
+    <t>manual</t>
+  </si>
+  <si>
+    <t>after</t>
   </si>
 </sst>
 </file>
@@ -828,10 +831,10 @@
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>106</v>
+      </c>
+      <c r="B2" s="1">
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -857,10 +860,10 @@
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>105</v>
+      </c>
+      <c r="B3" s="1">
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -886,9 +889,11 @@
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="B4" s="1">
+        <v>8</v>
+      </c>
       <c r="C4" t="s">
         <v>64</v>
       </c>
@@ -925,22 +930,25 @@
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="B6" s="1">
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
@@ -957,10 +965,10 @@
     </row>
     <row r="7" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>96</v>
+      </c>
+      <c r="B7" s="1">
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
@@ -992,10 +1000,13 @@
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="B8" s="1">
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="6"/>
       <c r="F8" s="1" t="s">
@@ -1017,7 +1028,7 @@
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>55</v>
@@ -1087,7 +1098,10 @@
     </row>
     <row r="13" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>25</v>
@@ -1113,7 +1127,10 @@
     </row>
     <row r="14" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>26</v>
@@ -1139,7 +1156,10 @@
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="B15" s="1">
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>27</v>
@@ -1165,7 +1185,10 @@
     </row>
     <row r="16" spans="1:13" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>28</v>
@@ -1193,6 +1216,9 @@
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="B17" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
@@ -1217,10 +1243,13 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>9</v>
@@ -1245,10 +1274,13 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>30</v>
@@ -1260,10 +1292,10 @@
         <v>68</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="17" t="s">
         <v>84</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>85</v>
       </c>
       <c r="I20" s="1">
         <v>2</v>
@@ -1280,7 +1312,10 @@
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>31</v>
@@ -1295,7 +1330,7 @@
         <v>68</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>51</v>
@@ -1315,10 +1350,10 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D22" s="6"/>
       <c r="F22" s="1" t="s">
@@ -1346,6 +1381,9 @@
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="B24" s="1">
+        <v>10</v>
+      </c>
       <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
@@ -1362,7 +1400,7 @@
         <v>33</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I24" s="1">
         <v>1</v>
@@ -1381,6 +1419,9 @@
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B25" s="1">
+        <v>30</v>
+      </c>
       <c r="C25" s="1" t="s">
         <v>35</v>
       </c>
@@ -1416,18 +1457,21 @@
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="B26" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="C26" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="6"/>
       <c r="F26" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I26" s="1">
         <v>1</v>
@@ -1445,6 +1489,9 @@
     <row r="27" spans="1:14" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>66</v>
@@ -1489,7 +1536,7 @@
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>38</v>
@@ -1514,6 +1561,9 @@
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B32" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="C32" s="1" t="s">
         <v>41</v>
       </c>
@@ -1527,10 +1577,10 @@
         <v>68</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="I32" s="1">
         <v>1</v>
@@ -1555,7 +1605,7 @@
     </row>
     <row r="35" spans="1:11" s="1" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D35" s="6"/>
       <c r="H35" s="6"/>
@@ -1638,10 +1688,10 @@
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H41" s="6"/>
     </row>
